--- a/output/roomself_excel/10010.xlsx
+++ b/output/roomself_excel/10010.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,11 +510,38 @@
       <c r="D2" t="n">
         <v>4724</v>
       </c>
-      <c r="E2" t="n">
-        <v>873</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>404</v>
+        <v>370</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1373</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>203</v>
+      </c>
+      <c r="M2" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +559,31 @@
       <c r="D3" t="n">
         <v>1568</v>
       </c>
-      <c r="E3" t="n">
-        <v>261</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>171</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="G3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>154</v>
+      </c>
+      <c r="J3" t="n">
+        <v>23</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
